--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,862 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132449805</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563061</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6566612</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132441853</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563043</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6566575</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132449079</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563106</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6566535</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132449751</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563058</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6566604</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132441686</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563143</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6566554</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer i äldre barrblandskog. Gammalt skogsbete med eneträd och trampgranar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132450433</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91313</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563092</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6566606</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer i sluttning ner mot hjälmaren i ett granbestånd. Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132449725</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563063</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6566602</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -1533,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132450433</v>
+        <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>91313</v>
+        <v>101304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,41 +1544,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563092</v>
+        <v>563063</v>
       </c>
       <c r="R9" t="n">
-        <v>6566606</v>
+        <v>6566602</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1610,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1625,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växer i sluttning ner mot hjälmaren i ett granbestånd. Äldre barrblandskog.</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132449725</v>
+        <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>101304</v>
+        <v>91313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,46 +1663,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563063</v>
+        <v>563092</v>
       </c>
       <c r="R10" t="n">
-        <v>6566602</v>
+        <v>6566606</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1734,7 +1729,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1744,7 +1739,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer i sluttning ner mot hjälmaren i ett granbestånd. Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132449079</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91313</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132449079</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91329</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132449079</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91331</v>
+        <v>91333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91333</v>
+        <v>91334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,6 +1768,345 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132965751</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563133</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6566535</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132968472</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563053</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6566526</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132969737</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91934</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vällbäck, Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6566404</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132449079</v>
       </c>
       <c r="B6" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>132965751</v>
       </c>
       <c r="B11" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>132968472</v>
       </c>
       <c r="B12" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>132969737</v>
       </c>
       <c r="B13" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>132969737</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>132449805</v>
       </c>
       <c r="B4" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>132441853</v>
       </c>
       <c r="B5" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132449079</v>
       </c>
       <c r="B6" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>132449751</v>
       </c>
       <c r="B7" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>132441686</v>
       </c>
       <c r="B8" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132449725</v>
       </c>
       <c r="B9" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>132450433</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>132965751</v>
       </c>
       <c r="B11" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>132968472</v>
       </c>
       <c r="B12" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>132969737</v>
       </c>
       <c r="B13" t="n">
-        <v>91938</v>
+        <v>91939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3327614</v>
+        <v>132450433</v>
       </c>
       <c r="B2" t="n">
-        <v>103087</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221101</v>
+        <v>4189</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öja, strax S om Vagnstaviken, Srm</t>
+          <t>Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563054.5428126378</v>
+        <v>563092</v>
       </c>
       <c r="R2" t="n">
-        <v>6566599.777655614</v>
+        <v>6566606</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H.Rydberg, Källskogsinventeringen</t>
+          <t>Växer i sluttning ner mot hjälmaren i ett granbestånd. Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,70 +778,71 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>översilad granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6217022</v>
+        <v>132447823</v>
       </c>
       <c r="B3" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öja, strax S om Vagnstaviken, Srm</t>
+          <t>Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563054.5428126378</v>
+        <v>563165</v>
       </c>
       <c r="R3" t="n">
-        <v>6566599.777655614</v>
+        <v>6566487</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,27 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>H.Rydberg, Källskogsinventeringen</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,81 +892,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>översilad granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132449805</v>
+        <v>132969737</v>
       </c>
       <c r="B4" t="n">
-        <v>101338</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Srm</t>
+          <t>Vällbäck, Vällbäck, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563061</v>
+        <v>563166</v>
       </c>
       <c r="R4" t="n">
-        <v>6566612</v>
+        <v>6566404</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +982,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132441853</v>
+        <v>132967840</v>
       </c>
       <c r="B5" t="n">
-        <v>101338</v>
+        <v>81031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,42 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6444</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Vällbäck, Srm</t>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563043</v>
+        <v>563100</v>
       </c>
       <c r="R5" t="n">
-        <v>6566575</v>
+        <v>6566588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,39 +1113,43 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132449079</v>
+        <v>132447171</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,46 +1157,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Srm</t>
+          <t>Vällbäck, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563106</v>
+        <v>563180</v>
       </c>
       <c r="R6" t="n">
-        <v>6566535</v>
+        <v>6566429</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1242,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132449751</v>
+        <v>132449079</v>
       </c>
       <c r="B7" t="n">
-        <v>101338</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,46 +1271,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563058</v>
+        <v>563106</v>
       </c>
       <c r="R7" t="n">
-        <v>6566604</v>
+        <v>6566535</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1361,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,60 +1379,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132441686</v>
+        <v>132965751</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Vällbäck, Srm</t>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563143</v>
+        <v>563133</v>
       </c>
       <c r="R8" t="n">
-        <v>6566554</v>
+        <v>6566535</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,27 +1453,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer i äldre barrblandskog. Gammalt skogsbete med eneträd och trampgranar.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,39 +1477,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132449725</v>
+        <v>132968472</v>
       </c>
       <c r="B9" t="n">
-        <v>101338</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,49 +1506,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Srm</t>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563063</v>
+        <v>563053</v>
       </c>
       <c r="R9" t="n">
-        <v>6566602</v>
+        <v>6566526</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,22 +1560,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,67 +1590,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132450433</v>
+        <v>2420625</v>
       </c>
       <c r="B10" t="n">
-        <v>91339</v>
+        <v>101897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4189</v>
+        <v>220075</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Srm</t>
+          <t>Öja, strax S om Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563092</v>
+        <v>563055</v>
       </c>
       <c r="R10" t="n">
-        <v>6566606</v>
+        <v>6566600</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1724,27 +1667,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2000-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2000-06-26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot hjälmaren i ett granbestånd. Äldre barrblandskog.</t>
+          <t>H.Rydberg, Källskogsinventeringen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,73 +1688,81 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>översilad granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132965751</v>
+        <v>132441686</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Vagnstaviken, Srm</t>
+          <t>Vagnstaviken, Vällbäck, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563133</v>
+        <v>563143</v>
       </c>
       <c r="R11" t="n">
-        <v>6566535</v>
+        <v>6566554</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1845,22 +1786,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer i äldre barrblandskog. Gammalt skogsbete med eneträd och trampgranar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,66 +1815,89 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132968472</v>
+        <v>132441748</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vagnstaviken, Vagnstaviken, Srm</t>
+          <t>Vagnstaviken, Vällbäck, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563053</v>
+        <v>563158</v>
       </c>
       <c r="R12" t="n">
-        <v>6566526</v>
+        <v>6566542</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,22 +1921,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,75 +1945,77 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132969737</v>
+        <v>3327614</v>
       </c>
       <c r="B13" t="n">
-        <v>91949</v>
+        <v>106061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>221101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällbäck, Vällbäck, Srm</t>
+          <t>Öja, strax S om Vagnstaviken, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563166</v>
+        <v>563055</v>
       </c>
       <c r="R13" t="n">
-        <v>6566404</v>
+        <v>6566600</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,22 +2039,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2000-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2000-06-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>H.Rydberg, Källskogsinventeringen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,19 +2060,935 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>översilad granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>109975330</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563179</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6566339</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, fuktig sluttning</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132968276</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104878</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221178</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bäckbräsma</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cardamine amara</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563068</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6566619</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Kent Hellström</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Kent Hellström</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132441853</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>563043</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6566575</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132449725</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>563063</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6566602</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132449751</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>563058</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6566604</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132449805</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>563061</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6566612</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>109975328</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vällbäck, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>563179</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6566339</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, fuktig sluttning</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6217022</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öja, strax S om Vagnstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>563055</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6566600</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2000-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2000-06-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>H.Rydberg, Källskogsinventeringen</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>översilad granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16119-2026 artfynd.xlsx
+++ b/artfynd/A 16119-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132450433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132447823</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132969737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132967840</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132447171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132449079</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1492,6 +1527,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132965751</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132968472</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2420625</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441686</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1971,6 +2026,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2078,6 +2138,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3327614</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2185,6 +2250,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109975330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132968276</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2418,6 +2493,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441853</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2537,6 +2617,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132449725</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2656,6 +2741,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132449751</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2775,6 +2865,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132449805</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2886,6 +2981,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109975328</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2989,8 +3089,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6217022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>